--- a/output/laminas_comunales/comunal_p_aps_a_2019_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_p_aps_a_2019_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,622 @@
         </is>
       </c>
       <c r="C2">
+        <v>85798.203125</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>85791.78125</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>77098.03125</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>76863.015625</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>75025.828125</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>74960.875</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>73861.3046875</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>73705.1953125</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>72280.9765625</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>71988.0078125</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>67631.953125</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>67384.3046875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>59320.359375</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>59144.51171875</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>46.9363250732422</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>46.8093757629395</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>46.4570541381836</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>46.41015625</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>45.4211044311523</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>45.4008750915527</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>45.1215438842773</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>45.0588989257812</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>44.6858711242676</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C25">
         <v>44.6427917480469</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>42.5397071838379</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>42.3795166015625</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>40.7427711486816</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>40.6704406738281</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>21.0363502502441</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>20.7216625213623</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>20.7008190155029</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>20.3872222900391</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>18.1119117736816</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>17.6157169342041</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>15.9245233535767</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>15.6779508590698</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>15.538646697998</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>15.4179649353027</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>11.5359334945679</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>11.3997116088867</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>9.562008857727051</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>9.38595771789551</v>
       </c>
     </row>
   </sheetData>
